--- a/artfynd/A 60881-2023 artfynd.xlsx
+++ b/artfynd/A 60881-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60881-2023 artfynd.xlsx
+++ b/artfynd/A 60881-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1538,6 +1538,130 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>101474664</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57095</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100100</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bivråk</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pernis apivorus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Motorbanan, Odensberg, Östersund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>490302</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7008117</v>
+      </c>
+      <c r="S9" t="n">
+        <v>23</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Hedenbo</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Hedenbo</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
